--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3030" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,6 +268,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">fr-documents-ajoutes-entries:La section contient au moins une entrée Document attaché (organizer) et au plus une entrée Simple observation (observation). {entry.where(organizer.exists()).count() &gt;= 1 and entry.where(observation.exists()).count() &lt;= 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -729,73 +733,36 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation</t>
-  </si>
-  <si>
-    <t>frSimpleObservation</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.nullFlavor</t>
+    <t>Entrée Simple observation (observation, 0..1) et entrées Document attaché (organizer, 1..*)</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.realmCode</t>
-  </si>
-  <si>
     <t>Section.entry.realmCode</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId</t>
-  </si>
-  <si>
     <t>Section.entry.typeId</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId.displayable</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.displayable</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId.root</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.root</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeId.extension</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.extension</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.templateId</t>
-  </si>
-  <si>
     <t>Section.entry.templateId</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.typeCode</t>
-  </si>
-  <si>
     <t>Section.entry.typeCode</t>
   </si>
   <si>
@@ -808,9 +775,6 @@
     <t>Entry.typeCode</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.contextConductionInd</t>
-  </si>
-  <si>
     <t>Section.entry.contextConductionInd</t>
   </si>
   <si>
@@ -818,9 +782,6 @@
   </si>
   <si>
     <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.act</t>
   </si>
   <si>
     <t>Section.entry.act</t>
@@ -833,9 +794,6 @@
     <t>Entry.act</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.encounter</t>
-  </si>
-  <si>
     <t>Section.entry.encounter</t>
   </si>
   <si>
@@ -846,9 +804,6 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
@@ -865,9 +820,6 @@
     <t>Entry.observation</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.observationMedia</t>
-  </si>
-  <si>
     <t>Section.entry.observationMedia</t>
   </si>
   <si>
@@ -878,20 +830,17 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organizer
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organizer {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-document-attache|0.1.0}
 </t>
   </si>
   <si>
+    <t>Entrée Document attaché</t>
+  </si>
+  <si>
     <t>Entry.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.procedure</t>
   </si>
   <si>
     <t>Section.entry.procedure</t>
@@ -904,9 +853,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -917,9 +863,6 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
@@ -930,9 +873,6 @@
     <t>Entry.substanceAdministration</t>
   </si>
   <si>
-    <t>Section.entry:frSimpleObservation.supply</t>
-  </si>
-  <si>
     <t>Section.entry.supply</t>
   </si>
   <si>
@@ -941,83 +881,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache</t>
-  </si>
-  <si>
-    <t>frDocumentAttache</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.organizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organizer {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-document-attache|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Document attaché</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.procedure</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frDocumentAttache.supply</t>
   </si>
   <si>
     <t>Section.component</t>
@@ -1390,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK96"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.06640625" customWidth="true" bestFit="true"/>
@@ -1641,25 +1504,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>81</v>
@@ -1677,11 +1540,11 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1708,11 +1571,11 @@
         <v>75</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>75</v>
@@ -1730,7 +1593,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>81</v>
@@ -1750,10 +1613,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1776,11 +1639,11 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1831,7 +1694,7 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -1851,10 +1714,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1877,11 +1740,11 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1932,7 +1795,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -1944,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -1952,17 +1815,17 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>81</v>
@@ -1980,11 +1843,11 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2011,11 +1874,11 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2033,7 +1896,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2053,17 +1916,17 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>81</v>
@@ -2081,11 +1944,11 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2136,7 +1999,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2156,17 +2019,17 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>81</v>
@@ -2184,11 +2047,11 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2239,7 +2102,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2259,17 +2122,17 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2287,11 +2150,11 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2300,7 +2163,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>75</v>
@@ -2342,7 +2205,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2362,17 +2225,17 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>76</v>
@@ -2390,11 +2253,11 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2445,7 +2308,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2465,10 +2328,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2491,11 +2354,11 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2534,17 +2397,17 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2564,13 +2427,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2592,13 +2455,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2649,7 +2512,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2669,17 +2532,17 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>81</v>
@@ -2697,11 +2560,11 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2728,11 +2591,11 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2750,7 +2613,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -2770,17 +2633,17 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>81</v>
@@ -2798,11 +2661,11 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2853,7 +2716,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -2873,17 +2736,17 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>81</v>
@@ -2901,11 +2764,11 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2956,7 +2819,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -2976,17 +2839,17 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>76</v>
@@ -3004,11 +2867,11 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3020,7 +2883,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3059,7 +2922,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3079,17 +2942,17 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>81</v>
@@ -3107,11 +2970,11 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3162,7 +3025,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3182,10 +3045,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3208,10 +3071,10 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -3263,7 +3126,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3283,10 +3146,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3309,7 +3172,7 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -3320,7 +3183,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3338,11 +3201,11 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3360,7 +3223,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3380,10 +3243,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3406,7 +3269,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -3417,7 +3280,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>75</v>
@@ -3435,11 +3298,11 @@
         <v>75</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -3457,7 +3320,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3477,10 +3340,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3494,7 +3357,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>75</v>
@@ -3503,13 +3366,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3560,7 +3423,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3580,10 +3443,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3597,7 +3460,7 @@
         <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>75</v>
@@ -3606,13 +3469,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3663,7 +3526,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -3683,17 +3546,17 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>81</v>
@@ -3711,11 +3574,11 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3742,11 +3605,11 @@
         <v>75</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>75</v>
@@ -3764,7 +3627,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -3784,10 +3647,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3812,11 +3675,11 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3828,7 +3691,7 @@
         <v>75</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>75</v>
@@ -3867,7 +3730,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -3887,17 +3750,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>76</v>
@@ -3915,11 +3778,11 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3931,7 +3794,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -3970,7 +3833,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -3990,17 +3853,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>81</v>
@@ -4018,11 +3881,11 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4034,7 +3897,7 @@
         <v>75</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>75</v>
@@ -4073,7 +3936,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4093,17 +3956,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>81</v>
@@ -4121,11 +3984,11 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4176,7 +4039,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4196,17 +4059,17 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>76</v>
@@ -4224,11 +4087,11 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4240,7 +4103,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4279,7 +4142,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4299,10 +4162,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4325,11 +4188,11 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4380,7 +4243,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4400,10 +4263,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4426,11 +4289,11 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4481,7 +4344,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4501,17 +4364,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>81</v>
@@ -4529,11 +4392,11 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4584,7 +4447,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4604,17 +4467,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>81</v>
@@ -4632,11 +4495,11 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4687,7 +4550,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4707,17 +4570,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>81</v>
@@ -4735,11 +4598,11 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4790,7 +4653,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4810,10 +4673,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4827,7 +4690,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -4836,17 +4699,17 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4895,7 +4758,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -4915,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4932,7 +4795,7 @@
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -4941,16 +4804,16 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5000,7 +4863,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5020,10 +4883,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5046,15 +4909,15 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5103,7 +4966,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5123,10 +4986,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5149,15 +5012,15 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5182,11 +5045,11 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -5204,7 +5067,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5224,10 +5087,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5250,17 +5113,17 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5309,7 +5172,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5329,10 +5192,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5355,13 +5218,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5410,7 +5273,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5430,10 +5293,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5456,13 +5319,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5511,7 +5374,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5529,12 +5392,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5548,7 +5411,7 @@
         <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>75</v>
@@ -5557,9 +5420,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="L41" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5598,17 +5463,19 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5628,18 +5495,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C42" t="s" s="2">
         <v>232</v>
       </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
@@ -5656,10 +5523,12 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5685,13 +5554,11 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -5709,13 +5576,13 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -5732,20 +5599,18 @@
         <v>233</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -5757,11 +5622,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5788,11 +5653,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -5810,13 +5677,13 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
@@ -5830,10 +5697,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5844,7 +5711,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -5856,11 +5723,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5911,19 +5778,19 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
@@ -5931,16 +5798,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
@@ -5957,11 +5826,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5988,13 +5857,11 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6012,7 +5879,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6024,7 +5891,7 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6032,17 +5899,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>81</v>
@@ -6060,11 +5927,11 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6091,11 +5958,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6113,7 +5982,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6133,17 +6002,17 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>81</v>
@@ -6161,11 +6030,11 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6216,7 +6085,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6236,20 +6105,20 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>76</v>
@@ -6264,11 +6133,11 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6277,7 +6146,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>75</v>
@@ -6319,7 +6188,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6339,17 +6208,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>76</v>
@@ -6367,11 +6236,11 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6380,7 +6249,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>75</v>
@@ -6422,7 +6291,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6442,23 +6311,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -6470,11 +6337,11 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6525,13 +6392,13 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
@@ -6545,10 +6412,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6559,7 +6426,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
@@ -6571,16 +6438,14 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L51" s="2"/>
-      <c r="M51" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
@@ -6602,13 +6467,11 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -6626,13 +6489,13 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>125</v>
+        <v>244</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
@@ -6646,10 +6509,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6672,18 +6535,18 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>75</v>
@@ -6701,11 +6564,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6723,7 +6588,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6743,10 +6608,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6769,7 +6634,7 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6780,7 +6645,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>75</v>
@@ -6822,7 +6687,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6842,10 +6707,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6868,7 +6733,7 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6921,7 +6786,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -6941,10 +6806,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6967,10 +6832,14 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7020,7 +6889,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7040,10 +6909,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7066,14 +6935,10 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7123,7 +6988,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7143,10 +7008,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7169,9 +7034,11 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="L57" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7222,7 +7089,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7242,10 +7109,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7268,7 +7135,7 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7321,7 +7188,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7341,10 +7208,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7367,7 +7234,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7420,7 +7287,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7440,10 +7307,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7466,7 +7333,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7519,7 +7386,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7406,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7565,7 +7432,7 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7618,7 +7485,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7638,10 +7505,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7652,7 +7519,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -7664,12 +7531,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L62" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>75</v>
       </c>
@@ -7717,13 +7588,13 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
@@ -7737,23 +7608,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -7765,10 +7636,12 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -7794,13 +7667,11 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -7818,13 +7689,13 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
@@ -7838,23 +7709,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
@@ -7866,11 +7735,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7897,11 +7766,13 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -7919,13 +7790,13 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
@@ -7939,10 +7810,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7953,7 +7824,7 @@
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
@@ -7965,11 +7836,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8020,19 +7891,19 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -8040,16 +7911,18 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F66" t="s" s="2">
         <v>81</v>
       </c>
@@ -8066,11 +7939,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8097,13 +7970,11 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8121,7 +7992,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8133,7 +8004,7 @@
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -8141,17 +8012,17 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>81</v>
@@ -8169,11 +8040,11 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8200,11 +8071,13 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -8222,7 +8095,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8242,17 +8115,17 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>81</v>
@@ -8270,11 +8143,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8325,7 +8198,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8345,20 +8218,20 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>76</v>
@@ -8373,11 +8246,11 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8386,7 +8259,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>75</v>
@@ -8428,7 +8301,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8448,17 +8321,17 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>76</v>
@@ -8476,11 +8349,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8489,7 +8362,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>75</v>
@@ -8531,7 +8404,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8551,23 +8424,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
@@ -8579,11 +8450,11 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8634,13 +8505,13 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>75</v>
@@ -8654,10 +8525,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8668,7 +8539,7 @@
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>75</v>
@@ -8680,11 +8551,11 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>122</v>
+        <v>292</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8693,7 +8564,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>75</v>
@@ -8735,13 +8606,13 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>125</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>75</v>
@@ -8755,10 +8626,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8781,18 +8652,18 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>75</v>
@@ -8810,11 +8681,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -8832,7 +8705,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8852,10 +8725,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8863,7 +8736,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>76</v>
@@ -8878,7 +8751,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>108</v>
+        <v>295</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8889,7 +8762,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>75</v>
@@ -8931,10 +8804,10 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
@@ -8949,2220 +8822,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y85" s="2"/>
-      <c r="Z85" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y88" s="2"/>
-      <c r="Z88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK96">
+  <autoFilter ref="A1:AK74">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11172,7 +8833,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-documents-ajoutes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
